--- a/docs/StructureDefinition-eva-suit-provisioning-record.xlsx
+++ b/docs/StructureDefinition-eva-suit-provisioning-record.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.0</t>
+    <t>0.6.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-25T15:07:02-06:00</t>
+    <t>2026-08-03T22:31:50-05:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-eva-suit-provisioning-record.xlsx
+++ b/docs/StructureDefinition-eva-suit-provisioning-record.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1039" uniqueCount="259">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1040" uniqueCount="260">
   <si>
     <t>Property</t>
   </si>
@@ -27,13 +27,13 @@
     <t>URL</t>
   </si>
   <si>
-    <t>https://mitre.org/fhir/space-health/StructureDefinition/eva-suit-provisioning-record</t>
+    <t>https://awatson1978.github.io/aerospace-medicine-ig/StructureDefinition/eva-suit-provisioning-record</t>
   </si>
   <si>
     <t>Version</t>
   </si>
   <si>
-    <t>0.6.2</t>
+    <t>0.7.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-03T22:31:50-05:00</t>
+    <t>2026-09-02T13:24:45-05:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -91,6 +91,9 @@
   </si>
   <si>
     <t>Copyright</t>
+  </si>
+  <si>
+    <t>Copyright 2022-2026 The MITRE Corporation and Abigail Watson. Licensed under Creative Commons Attribution-NoDerivatives 4.0 International (CC BY-ND 4.0). Approved for Public Release; Distribution Unlimited. Public Release Case Number 25-1124.</t>
   </si>
   <si>
     <t>FHIR Version</t>
@@ -452,7 +455,7 @@
     <t>missionContext</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://hl7.org/fhir/uv/aerospace/StructureDefinition/mission-context}
+    <t xml:space="preserve">Extension {https://awatson1978.github.io/aerospace-medicine-ig/StructureDefinition/mission-context}
 </t>
   </si>
   <si>
@@ -1089,54 +1092,56 @@
       <c r="A14" t="s" s="2">
         <v>24</v>
       </c>
-      <c r="B14" s="2"/>
+      <c r="B14" t="s" s="2">
+        <v>25</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
   </sheetData>
@@ -1159,7 +1164,7 @@
     <col min="8" max="8" width="12.6875" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="10.51171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="64.3359375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="81.42578125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1192,132 +1197,132 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s" s="1">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B1" t="s" s="1">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C1" t="s" s="1">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="D1" t="s" s="1">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E1" t="s" s="1">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F1" t="s" s="1">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="G1" t="s" s="1">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H1" t="s" s="1">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="I1" t="s" s="1">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="J1" t="s" s="1">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K1" t="s" s="1">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L1" t="s" s="1">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M1" t="s" s="1">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N1" t="s" s="1">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="O1" t="s" s="1">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="P1" t="s" s="1">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="Q1" t="s" s="1">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="R1" t="s" s="1">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="S1" t="s" s="1">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="T1" t="s" s="1">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="U1" t="s" s="1">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="V1" t="s" s="1">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="W1" t="s" s="1">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="X1" t="s" s="1">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="Y1" t="s" s="1">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Z1" t="s" s="1">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="AA1" t="s" s="1">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="AB1" t="s" s="1">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="AC1" t="s" s="1">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="AD1" t="s" s="1">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="AE1" t="s" s="1">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AF1" t="s" s="1">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="AG1" t="s" s="1">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="AH1" t="s" s="1">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="AI1" t="s" s="1">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="AJ1" t="s" s="1">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="AK1" t="s" s="1">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="AL1" t="s" s="1">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="AM1" t="s" s="1">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="AN1" t="s" s="1">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" t="s" s="2">
@@ -1325,10 +1330,10 @@
       </c>
       <c r="E2" s="2"/>
       <c r="F2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G2" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H2" t="s" s="2">
         <v>20</v>
@@ -1340,13 +1345,13 @@
         <v>20</v>
       </c>
       <c r="K2" t="s" s="2">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="L2" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M2" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
@@ -1397,25 +1402,25 @@
         <v>20</v>
       </c>
       <c r="AF2" t="s" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="AG2" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH2" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI2" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ2" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AK2" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="AL2" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="AM2" t="s" s="2">
         <v>20</v>
@@ -1426,10 +1431,10 @@
     </row>
     <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" t="s" s="2">
@@ -1437,10 +1442,10 @@
       </c>
       <c r="E3" s="2"/>
       <c r="F3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H3" t="s" s="2">
         <v>20</v>
@@ -1449,19 +1454,19 @@
         <v>20</v>
       </c>
       <c r="J3" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K3" t="s" s="2">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="L3" t="s" s="2">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N3" t="s" s="2">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="O3" s="2"/>
       <c r="P3" t="s" s="2">
@@ -1511,13 +1516,13 @@
         <v>20</v>
       </c>
       <c r="AF3" t="s" s="2">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="AG3" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH3" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI3" t="s" s="2">
         <v>20</v>
@@ -1540,10 +1545,10 @@
     </row>
     <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -1551,10 +1556,10 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>20</v>
@@ -1563,16 +1568,16 @@
         <v>20</v>
       </c>
       <c r="J4" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1623,19 +1628,19 @@
         <v>20</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ4" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK4" t="s" s="2">
         <v>20</v>
@@ -1652,10 +1657,10 @@
     </row>
     <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1663,31 +1668,31 @@
       </c>
       <c r="E5" s="2"/>
       <c r="F5" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G5" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I5" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J5" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N5" t="s" s="2">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="O5" s="2"/>
       <c r="P5" t="s" s="2">
@@ -1737,19 +1742,19 @@
         <v>20</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AG5" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH5" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI5" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ5" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK5" t="s" s="2">
         <v>20</v>
@@ -1766,10 +1771,10 @@
     </row>
     <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B6" t="s" s="2">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C6" s="2"/>
       <c r="D6" t="s" s="2">
@@ -1777,10 +1782,10 @@
       </c>
       <c r="E6" s="2"/>
       <c r="F6" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G6" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H6" t="s" s="2">
         <v>20</v>
@@ -1792,16 +1797,16 @@
         <v>20</v>
       </c>
       <c r="K6" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L6" t="s" s="2">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M6" t="s" s="2">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N6" t="s" s="2">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="O6" s="2"/>
       <c r="P6" t="s" s="2">
@@ -1827,13 +1832,13 @@
         <v>20</v>
       </c>
       <c r="X6" t="s" s="2">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="Y6" t="s" s="2">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="Z6" t="s" s="2">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="AA6" t="s" s="2">
         <v>20</v>
@@ -1851,19 +1856,19 @@
         <v>20</v>
       </c>
       <c r="AF6" t="s" s="2">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="AG6" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH6" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI6" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ6" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK6" t="s" s="2">
         <v>20</v>
@@ -1880,21 +1885,21 @@
     </row>
     <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B7" t="s" s="2">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" t="s" s="2">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E7" s="2"/>
       <c r="F7" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G7" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H7" t="s" s="2">
         <v>20</v>
@@ -1906,16 +1911,16 @@
         <v>20</v>
       </c>
       <c r="K7" t="s" s="2">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="L7" t="s" s="2">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="M7" t="s" s="2">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="N7" t="s" s="2">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="O7" s="2"/>
       <c r="P7" t="s" s="2">
@@ -1965,25 +1970,25 @@
         <v>20</v>
       </c>
       <c r="AF7" t="s" s="2">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AG7" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH7" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI7" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ7" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK7" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL7" t="s" s="2">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AM7" t="s" s="2">
         <v>20</v>
@@ -1994,21 +1999,21 @@
     </row>
     <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B8" t="s" s="2">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" t="s" s="2">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="E8" s="2"/>
       <c r="F8" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G8" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H8" t="s" s="2">
         <v>20</v>
@@ -2020,16 +2025,16 @@
         <v>20</v>
       </c>
       <c r="K8" t="s" s="2">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="L8" t="s" s="2">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="M8" t="s" s="2">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N8" t="s" s="2">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O8" s="2"/>
       <c r="P8" t="s" s="2">
@@ -2079,13 +2084,13 @@
         <v>20</v>
       </c>
       <c r="AF8" t="s" s="2">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="AG8" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH8" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI8" t="s" s="2">
         <v>20</v>
@@ -2097,7 +2102,7 @@
         <v>20</v>
       </c>
       <c r="AL8" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AM8" t="s" s="2">
         <v>20</v>
@@ -2108,10 +2113,10 @@
     </row>
     <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B9" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" t="s" s="2">
@@ -2119,10 +2124,10 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G9" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H9" t="s" s="2">
         <v>20</v>
@@ -2134,13 +2139,13 @@
         <v>20</v>
       </c>
       <c r="K9" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L9" t="s" s="2">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="M9" t="s" s="2">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="N9" s="2"/>
       <c r="O9" s="2"/>
@@ -2179,29 +2184,29 @@
         <v>20</v>
       </c>
       <c r="AB9" t="s" s="2">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AC9" s="2"/>
       <c r="AD9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE9" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AF9" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AG9" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH9" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI9" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ9" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AK9" t="s" s="2">
         <v>20</v>
@@ -2218,26 +2223,26 @@
     </row>
     <row r="10">
       <c r="A10" t="s" s="2">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B10" t="s" s="2">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C10" t="s" s="2">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="D10" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E10" s="2"/>
       <c r="F10" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G10" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H10" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I10" t="s" s="2">
         <v>20</v>
@@ -2246,13 +2251,13 @@
         <v>20</v>
       </c>
       <c r="K10" t="s" s="2">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="L10" t="s" s="2">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="M10" t="s" s="2">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="N10" s="2"/>
       <c r="O10" s="2"/>
@@ -2303,19 +2308,19 @@
         <v>20</v>
       </c>
       <c r="AF10" t="s" s="2">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AG10" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH10" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="AJ10" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AK10" t="s" s="2">
         <v>20</v>
@@ -2332,45 +2337,45 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G11" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I11" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="K11" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>20</v>
@@ -2419,25 +2424,25 @@
         <v>20</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="AG11" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH11" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ11" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AK11" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL11" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AM11" t="s" s="2">
         <v>20</v>
@@ -2448,10 +2453,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2459,10 +2464,10 @@
       </c>
       <c r="E12" s="2"/>
       <c r="F12" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G12" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H12" t="s" s="2">
         <v>20</v>
@@ -2474,16 +2479,16 @@
         <v>20</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="O12" s="2"/>
       <c r="P12" t="s" s="2">
@@ -2533,25 +2538,25 @@
         <v>20</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG12" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH12" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI12" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ12" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="AL12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="AM12" t="s" s="2">
         <v>20</v>
@@ -2562,10 +2567,10 @@
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2573,10 +2578,10 @@
       </c>
       <c r="E13" s="2"/>
       <c r="F13" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H13" t="s" s="2">
         <v>20</v>
@@ -2585,20 +2590,20 @@
         <v>20</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="N13" s="2"/>
       <c r="O13" t="s" s="2">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="P13" t="s" s="2">
         <v>20</v>
@@ -2647,28 +2652,28 @@
         <v>20</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="AG13" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI13" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="AN13" t="s" s="2">
         <v>20</v>
@@ -2676,10 +2681,10 @@
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2687,10 +2692,10 @@
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G14" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H14" t="s" s="2">
         <v>20</v>
@@ -2699,22 +2704,22 @@
         <v>20</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="N14" t="s" s="2">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O14" t="s" s="2">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="P14" t="s" s="2">
         <v>20</v>
@@ -2763,28 +2768,28 @@
         <v>20</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="AG14" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH14" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI14" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AN14" t="s" s="2">
         <v>20</v>
@@ -2792,10 +2797,10 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -2803,31 +2808,31 @@
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G15" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I15" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J15" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -2853,13 +2858,13 @@
         <v>20</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>20</v>
@@ -2877,25 +2882,25 @@
         <v>20</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="AG15" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH15" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI15" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AM15" t="s" s="2">
         <v>20</v>
@@ -2906,10 +2911,10 @@
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -2917,10 +2922,10 @@
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H16" t="s" s="2">
         <v>20</v>
@@ -2932,13 +2937,13 @@
         <v>20</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -2989,25 +2994,25 @@
         <v>20</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AG16" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="AM16" t="s" s="2">
         <v>20</v>
@@ -3018,10 +3023,10 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3029,13 +3034,13 @@
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G17" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H17" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I17" t="s" s="2">
         <v>20</v>
@@ -3044,13 +3049,13 @@
         <v>20</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3077,13 +3082,13 @@
         <v>20</v>
       </c>
       <c r="X17" t="s" s="2">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="Y17" t="s" s="2">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Z17" t="s" s="2">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="AA17" t="s" s="2">
         <v>20</v>
@@ -3101,25 +3106,25 @@
         <v>20</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="AG17" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH17" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI17" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK17" t="s" s="2">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>20</v>
@@ -3130,10 +3135,10 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3141,13 +3146,13 @@
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G18" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H18" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I18" t="s" s="2">
         <v>20</v>
@@ -3156,13 +3161,13 @@
         <v>20</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" s="2"/>
@@ -3213,25 +3218,25 @@
         <v>20</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="AG18" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH18" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ18" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK18" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>20</v>
@@ -3242,10 +3247,10 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3253,10 +3258,10 @@
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G19" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H19" t="s" s="2">
         <v>20</v>
@@ -3268,13 +3273,13 @@
         <v>20</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
@@ -3325,13 +3330,13 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="AG19" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH19" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI19" t="s" s="2">
         <v>20</v>
@@ -3343,7 +3348,7 @@
         <v>20</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>20</v>
@@ -3354,21 +3359,21 @@
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E20" s="2"/>
       <c r="F20" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G20" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H20" t="s" s="2">
         <v>20</v>
@@ -3380,16 +3385,16 @@
         <v>20</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -3439,25 +3444,25 @@
         <v>20</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="AG20" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH20" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AK20" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>20</v>
@@ -3468,45 +3473,45 @@
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="I21" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>20</v>
@@ -3555,25 +3560,25 @@
         <v>20</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="AG21" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AK21" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>20</v>
@@ -3584,10 +3589,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3595,13 +3600,13 @@
       </c>
       <c r="E22" s="2"/>
       <c r="F22" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H22" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I22" t="s" s="2">
         <v>20</v>
@@ -3610,13 +3615,13 @@
         <v>20</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="N22" s="2"/>
       <c r="O22" s="2"/>
@@ -3667,25 +3672,25 @@
         <v>20</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="AG22" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ22" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK22" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>20</v>
@@ -3696,10 +3701,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -3707,13 +3712,13 @@
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>20</v>
@@ -3722,13 +3727,13 @@
         <v>20</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" s="2"/>
@@ -3755,13 +3760,13 @@
         <v>20</v>
       </c>
       <c r="X23" t="s" s="2">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>20</v>
@@ -3779,25 +3784,25 @@
         <v>20</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="AG23" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK23" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>20</v>
@@ -3808,10 +3813,10 @@
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -3819,10 +3824,10 @@
       </c>
       <c r="E24" s="2"/>
       <c r="F24" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H24" t="s" s="2">
         <v>20</v>
@@ -3831,19 +3836,19 @@
         <v>20</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -3881,83 +3886,83 @@
         <v>20</v>
       </c>
       <c r="AB24" t="s" s="2">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="AC24" s="2"/>
       <c r="AD24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE24" t="s" s="2">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AG24" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI24" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AN24" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="C25" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="E25" s="2"/>
       <c r="F25" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G25" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H25" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="J25" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4007,39 +4012,39 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="AG25" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH25" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI25" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="AN25" t="s" s="2">
-        <v>238</v>
+        <v>239</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4047,10 +4052,10 @@
       </c>
       <c r="E26" s="2"/>
       <c r="F26" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>20</v>
@@ -4062,13 +4067,13 @@
         <v>20</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" s="2"/>
@@ -4119,25 +4124,25 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AG26" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>20</v>
@@ -4148,10 +4153,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4159,13 +4164,13 @@
       </c>
       <c r="E27" s="2"/>
       <c r="F27" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G27" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>20</v>
@@ -4174,13 +4179,13 @@
         <v>20</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4231,25 +4236,25 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="AG27" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH27" t="s" s="2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="AI27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK27" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>20</v>
@@ -4260,10 +4265,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4271,10 +4276,10 @@
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>20</v>
@@ -4286,13 +4291,13 @@
         <v>20</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4343,25 +4348,25 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="AG28" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="AK28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>20</v>
